--- a/alunos_matricula.xlsx
+++ b/alunos_matricula.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="11580"/>
+    <workbookView windowWidth="28800" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="Alunos" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
   <si>
     <t>Matrícula</t>
   </si>
@@ -237,6 +237,24 @@
   </si>
   <si>
     <t>21:00</t>
+  </si>
+  <si>
+    <t>João Vitor</t>
+  </si>
+  <si>
+    <t>pedreiro</t>
+  </si>
+  <si>
+    <t>sim</t>
+  </si>
+  <si>
+    <t>nenhuma</t>
+  </si>
+  <si>
+    <t>c301</t>
+  </si>
+  <si>
+    <t>Jhonathan</t>
   </si>
 </sst>
 </file>
@@ -857,8 +875,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1205,7 +1224,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13.1428571428571" customWidth="1"/>
@@ -1567,6 +1586,38 @@
         <v>18</v>
       </c>
     </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>20168</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12">
+        <v>9999</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/alunos_matricula.xlsx
+++ b/alunos_matricula.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30110"/>
   <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{664E070E-D63F-4C22-9C9A-822477B7BB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15810" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alunos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
   <si>
     <t>Matrícula</t>
   </si>
@@ -230,9 +234,6 @@
     <t>Gustavo Almeida</t>
   </si>
   <si>
-    <t>8888</t>
-  </si>
-  <si>
     <t>D201</t>
   </si>
   <si>
@@ -251,7 +252,7 @@
     <t>nenhuma</t>
   </si>
   <si>
-    <t>c301</t>
+    <t>C301</t>
   </si>
   <si>
     <t>Jhonathan</t>
@@ -260,14 +261,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,353 +270,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -629,311 +287,30 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
-    <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Moeda [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Hyperlink seguido" xfId="7" builtinId="9"/>
-    <cellStyle name="Observação" xfId="8" builtinId="10"/>
-    <cellStyle name="Texto de Aviso" xfId="9" builtinId="11"/>
-    <cellStyle name="Título" xfId="10" builtinId="15"/>
-    <cellStyle name="Texto Explicativo" xfId="11" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
-    <cellStyle name="Saída" xfId="17" builtinId="21"/>
-    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
-    <cellStyle name="Célula de Verificação" xfId="19" builtinId="23"/>
-    <cellStyle name="Célula Vinculada" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Bom" xfId="22" builtinId="26"/>
-    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
-    <cellStyle name="Ênfase 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Ênfase 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Ênfase 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Ênfase 1" xfId="28" builtinId="32"/>
-    <cellStyle name="Ênfase 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Ênfase 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Ênfase 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Ênfase 2" xfId="32" builtinId="36"/>
-    <cellStyle name="Ênfase 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Ênfase 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Ênfase 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Ênfase 3" xfId="36" builtinId="40"/>
-    <cellStyle name="Ênfase 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Ênfase 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Ênfase 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Ênfase 4" xfId="40" builtinId="44"/>
-    <cellStyle name="Ênfase 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Ênfase 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Ênfase 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Ênfase 5" xfId="44" builtinId="48"/>
-    <cellStyle name="Ênfase 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Ênfase 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Ênfase 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1218,20 +595,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="10.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="20.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="18.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="18.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="18.375" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1561,8 +939,8 @@
       <c r="B11" t="s">
         <v>66</v>
       </c>
-      <c r="C11" t="s">
-        <v>67</v>
+      <c r="C11" s="1">
+        <v>8888</v>
       </c>
       <c r="D11" t="s">
         <v>37</v>
@@ -1574,10 +952,10 @@
         <v>38</v>
       </c>
       <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
         <v>68</v>
-      </c>
-      <c r="H11" t="s">
-        <v>69</v>
       </c>
       <c r="I11" t="s">
         <v>41</v>
@@ -1591,28 +969,28 @@
         <v>20168</v>
       </c>
       <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="1">
+        <v>9999</v>
+      </c>
+      <c r="D12" t="s">
         <v>70</v>
       </c>
-      <c r="C12">
-        <v>9999</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>71</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>72</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>73</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" s="2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="I12" t="s">
         <v>74</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="I12" t="s">
-        <v>75</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -1620,6 +998,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/alunos_matricula.xlsx
+++ b/alunos_matricula.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30110"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{664E070E-D63F-4C22-9C9A-822477B7BB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E15D952-B477-4ED1-A001-FB5467D5FE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15810" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
   <si>
     <t>Matrícula</t>
   </si>
@@ -243,13 +243,7 @@
     <t>João Vitor</t>
   </si>
   <si>
-    <t>pedreiro</t>
-  </si>
-  <si>
-    <t>sim</t>
-  </si>
-  <si>
-    <t>nenhuma</t>
+    <t>Pedreiro</t>
   </si>
   <si>
     <t>C301</t>
@@ -609,6 +603,7 @@
     <col min="4" max="4" width="20.625" customWidth="1"/>
     <col min="5" max="5" width="18.375" customWidth="1"/>
     <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="8" max="8" width="10.875" customWidth="1"/>
     <col min="10" max="10" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -978,19 +973,19 @@
         <v>70</v>
       </c>
       <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
         <v>71</v>
-      </c>
-      <c r="F12" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" t="s">
-        <v>73</v>
       </c>
       <c r="H12" s="2">
         <v>0.77083333333333304</v>
       </c>
       <c r="I12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>

--- a/alunos_matricula.xlsx
+++ b/alunos_matricula.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30110"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E15D952-B477-4ED1-A001-FB5467D5FE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20023CB7-C87D-4C19-BF3C-E26F46112C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15810" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
   <si>
     <t>Matrícula</t>
   </si>
@@ -250,19 +250,37 @@
   </si>
   <si>
     <t>Jhonathan</t>
+  </si>
+  <si>
+    <t>Loran</t>
+  </si>
+  <si>
+    <t>Todos</t>
+  </si>
+  <si>
+    <t>F123</t>
+  </si>
+  <si>
+    <t>Marcos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -285,12 +303,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -595,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -991,6 +1016,38 @@
         <v>18</v>
       </c>
     </row>
+    <row r="13" spans="1:10" ht="13.5">
+      <c r="A13" s="3">
+        <v>1232</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1672</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.78125</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/alunos_matricula.xlsx
+++ b/alunos_matricula.xlsx
@@ -1,276 +1,446 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="5"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="14400" windowHeight="11580" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Alunos" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Alunos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
-  <si>
-    <t xml:space="preserve">Matrícula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrícula Ativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendências</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sala Atual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horário Aula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensalidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">João Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Histórico escolar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em dia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Oliveira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administração</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comprovante de residência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ana Souza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Santos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enfermagem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RG e CPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernanda Lima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em atraso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Ferreira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engenharia Civil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nenhuma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberto Alves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juliana Costa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foto 3x4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariana Rocha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Gomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrato assinado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beatriz Martins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psicologia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paula Mendes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felipe Ribeiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camila Fernandes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carteira de vacinação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gustavo Almeida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:00</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+  <si>
+    <t>Matrícula</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Senha</t>
+  </si>
+  <si>
+    <t>Curso</t>
+  </si>
+  <si>
+    <t>Matrícula Ativa</t>
+  </si>
+  <si>
+    <t>Pendências</t>
+  </si>
+  <si>
+    <t>Sala Atual</t>
+  </si>
+  <si>
+    <t>Horário Aula</t>
+  </si>
+  <si>
+    <t>Professor</t>
+  </si>
+  <si>
+    <t>Mensalidade</t>
+  </si>
+  <si>
+    <t>João Silva</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>Informática</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Histórico escolar</t>
+  </si>
+  <si>
+    <t>B203</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>Carlos Silva</t>
+  </si>
+  <si>
+    <t>Em dia</t>
+  </si>
+  <si>
+    <t>Maria Oliveira</t>
+  </si>
+  <si>
+    <t>5678</t>
+  </si>
+  <si>
+    <t>Administração</t>
+  </si>
+  <si>
+    <t>Comprovante de residência</t>
+  </si>
+  <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>Ana Souza</t>
+  </si>
+  <si>
+    <t>Pedro Santos</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>Enfermagem</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>RG e CPF</t>
+  </si>
+  <si>
+    <t>C305</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>Fernanda Lima</t>
+  </si>
+  <si>
+    <t>Em atraso</t>
+  </si>
+  <si>
+    <t>Lucas Ferreira</t>
+  </si>
+  <si>
+    <t>2222</t>
+  </si>
+  <si>
+    <t>Engenharia Civil</t>
+  </si>
+  <si>
+    <t>Nenhuma</t>
+  </si>
+  <si>
+    <t>D102</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>Roberto Alves</t>
+  </si>
+  <si>
+    <t>Juliana Costa</t>
+  </si>
+  <si>
+    <t>3333</t>
+  </si>
+  <si>
+    <t>Direito</t>
+  </si>
+  <si>
+    <t>Foto 3x4</t>
+  </si>
+  <si>
+    <t>B101</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>Mariana Rocha</t>
+  </si>
+  <si>
+    <t>Rafael Gomes</t>
+  </si>
+  <si>
+    <t>4444</t>
+  </si>
+  <si>
+    <t>Contrato assinado</t>
+  </si>
+  <si>
+    <t>Lab 2</t>
+  </si>
+  <si>
+    <t>Beatriz Martins</t>
+  </si>
+  <si>
+    <t>5555</t>
+  </si>
+  <si>
+    <t>Psicologia</t>
+  </si>
+  <si>
+    <t>E202</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>Paula Mendes</t>
+  </si>
+  <si>
+    <t>Felipe Ribeiro</t>
+  </si>
+  <si>
+    <t>6666</t>
+  </si>
+  <si>
+    <t>A202</t>
+  </si>
+  <si>
+    <t>Camila Fernandes</t>
+  </si>
+  <si>
+    <t>7777</t>
+  </si>
+  <si>
+    <t>Carteira de vacinação</t>
+  </si>
+  <si>
+    <t>C101</t>
+  </si>
+  <si>
+    <t>Gustavo Almeida</t>
+  </si>
+  <si>
+    <t>8888</t>
+  </si>
+  <si>
+    <t>D201</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>jorge</t>
+  </si>
+  <si>
+    <t>pedreiro</t>
+  </si>
+  <si>
+    <t>não</t>
+  </si>
+  <si>
+    <t>nenhuma</t>
+  </si>
+  <si>
+    <t>f312</t>
+  </si>
+  <si>
+    <t>lucas</t>
+  </si>
+  <si>
+    <t>em dia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;* #,##0_-;\-&quot;R$&quot;* #,##0_-;_-&quot;R$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -283,132 +453,792 @@
         <bgColor rgb="FF800000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="9">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
+    <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Moeda [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Hyperlink seguido" xfId="7" builtinId="9"/>
+    <cellStyle name="Observação" xfId="8" builtinId="10"/>
+    <cellStyle name="Texto de Aviso" xfId="9" builtinId="11"/>
+    <cellStyle name="Título" xfId="10" builtinId="15"/>
+    <cellStyle name="Texto Explicativo" xfId="11" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
+    <cellStyle name="Saída" xfId="17" builtinId="21"/>
+    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
+    <cellStyle name="Célula de Verificação" xfId="19" builtinId="23"/>
+    <cellStyle name="Célula Vinculada" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Bom" xfId="22" builtinId="26"/>
+    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
+    <cellStyle name="Ênfase 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Ênfase 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Ênfase 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Ênfase 1" xfId="28" builtinId="32"/>
+    <cellStyle name="Ênfase 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Ênfase 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Ênfase 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Ênfase 2" xfId="32" builtinId="36"/>
+    <cellStyle name="Ênfase 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Ênfase 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Ênfase 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Ênfase 3" xfId="36" builtinId="40"/>
+    <cellStyle name="Ênfase 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Ênfase 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Ênfase 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Ênfase 4" xfId="40" builtinId="44"/>
+    <cellStyle name="Ênfase 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Ênfase 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Ênfase 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Ênfase 5" xfId="44" builtinId="48"/>
+    <cellStyle name="Ênfase 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Ênfase 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Ênfase 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF6D1D20"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="006D1D20"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -450,17 +1280,17 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,7 +1314,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -505,7 +1335,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -556,7 +1386,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -574,34 +1404,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.19"/>
+    <col min="2" max="2" width="16.5428571428571" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5714285714286" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5714285714286" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.4285714285714" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.4761904761905" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.152380952381" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.1809523809524" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.3428571428571" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1904761904762" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -633,8 +1462,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:10">
+      <c r="A2" s="3">
         <v>1001</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -665,8 +1494,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:10">
+      <c r="A3" s="3">
         <v>1002</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -697,8 +1526,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:10">
+      <c r="A4" s="3">
         <v>1003</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -729,8 +1558,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:10">
+      <c r="A5" s="3">
         <v>1004</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -761,8 +1590,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:10">
+      <c r="A6" s="3">
         <v>1005</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -793,8 +1622,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:10">
+      <c r="A7" s="3">
         <v>1006</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -825,8 +1654,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:10">
+      <c r="A8" s="3">
         <v>1007</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -857,8 +1686,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+    <row r="9" spans="1:10">
+      <c r="A9" s="3">
         <v>1008</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -889,8 +1718,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+    <row r="10" spans="1:10">
+      <c r="A10" s="3">
         <v>1009</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -921,8 +1750,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+    <row r="11" spans="1:10">
+      <c r="A11" s="3">
         <v>1010</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -953,13 +1782,41 @@
         <v>18</v>
       </c>
     </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>1362</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="1">
+        <v>9999</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.8125</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>